--- a/data/trans_orig/POLIPATOLOGIA_Lim_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_2-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2012</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108017</t>
+          <t>108736</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>148252</t>
+          <t>152039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>204823</t>
+          <t>206858</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>255223</t>
+          <t>256465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>323356</t>
+          <t>325833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>393140</t>
+          <t>392772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>555217</t>
+          <t>551430</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>595452</t>
+          <t>594733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>441827</t>
+          <t>440585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>492227</t>
+          <t>490192</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1007379</t>
+          <t>1007747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1077163</t>
+          <t>1074686</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,73%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>151333</t>
+          <t>151594</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>203224</t>
+          <t>200868</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>282389</t>
+          <t>279617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>341757</t>
+          <t>340335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>447216</t>
+          <t>445783</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>530387</t>
+          <t>526171</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>814723</t>
+          <t>817079</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>866614</t>
+          <t>866353</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>690427</t>
+          <t>691849</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>749795</t>
+          <t>752567</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1519744</t>
+          <t>1523960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1602915</t>
+          <t>1604348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,26%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91442</t>
+          <t>91230</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132552</t>
+          <t>133992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>171362</t>
+          <t>174180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>224731</t>
+          <t>223471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>277765</t>
+          <t>279215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>345671</t>
+          <t>343222</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>625071</t>
+          <t>623631</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666181</t>
+          <t>666393</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>552443</t>
+          <t>553703</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>605812</t>
+          <t>602994</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1189126</t>
+          <t>1191575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1257032</t>
+          <t>1255582</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>145149</t>
+          <t>144221</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>195842</t>
+          <t>193174</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>269909</t>
+          <t>270174</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>332634</t>
+          <t>332070</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>429586</t>
+          <t>430553</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>508916</t>
+          <t>509160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>751897</t>
+          <t>754565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>802590</t>
+          <t>803518</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>719267</t>
+          <t>719831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>781992</t>
+          <t>781727</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1490724</t>
+          <t>1490480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1570054</t>
+          <t>1569087</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,47%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>539147</t>
+          <t>538765</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>628616</t>
+          <t>628083</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>985463</t>
+          <t>990630</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1095935</t>
+          <t>1099426</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1547932</t>
+          <t>1554153</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1698386</t>
+          <t>1693328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2798163</t>
+          <t>2798696</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2887632</t>
+          <t>2888014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2462374</t>
+          <t>2458883</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2572846</t>
+          <t>2567679</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5286702</t>
+          <t>5291760</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5437156</t>
+          <t>5430935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,75%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2016</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82985</t>
+          <t>85207</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120632</t>
+          <t>121846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>166649</t>
+          <t>167660</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>214384</t>
+          <t>214004</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>261354</t>
+          <t>261216</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>321902</t>
+          <t>323033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>554168</t>
+          <t>552954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>591815</t>
+          <t>589593</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>458455</t>
+          <t>458835</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>506190</t>
+          <t>505179</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1025737</t>
+          <t>1024606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1086285</t>
+          <t>1086423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,62%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132184</t>
+          <t>130610</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>177568</t>
+          <t>175570</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>240414</t>
+          <t>240631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>302054</t>
+          <t>301966</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>386280</t>
+          <t>389068</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>467479</t>
+          <t>465250</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>844863</t>
+          <t>846861</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>890247</t>
+          <t>891821</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>740859</t>
+          <t>740947</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>802499</t>
+          <t>802282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1597865</t>
+          <t>1600094</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1679064</t>
+          <t>1676276</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87321</t>
+          <t>87705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123512</t>
+          <t>124125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157878</t>
+          <t>160184</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207326</t>
+          <t>205434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256411</t>
+          <t>256131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>318885</t>
+          <t>316322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636040</t>
+          <t>635427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>672231</t>
+          <t>671847</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>577685</t>
+          <t>579577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>627133</t>
+          <t>624827</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1225678</t>
+          <t>1228241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1288152</t>
+          <t>1288432</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124338</t>
+          <t>125115</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>169081</t>
+          <t>170219</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>239339</t>
+          <t>239501</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>301136</t>
+          <t>299518</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>379909</t>
+          <t>379464</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>456674</t>
+          <t>456355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>768486</t>
+          <t>767348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>813229</t>
+          <t>812452</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>742643</t>
+          <t>744261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>804440</t>
+          <t>804278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1524672</t>
+          <t>1524991</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1601437</t>
+          <t>1601882</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>465684</t>
+          <t>464515</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>548403</t>
+          <t>548687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>858554</t>
+          <t>860858</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>967781</t>
+          <t>968200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1346697</t>
+          <t>1344647</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1488780</t>
+          <t>1484176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2845947</t>
+          <t>2845663</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2928666</t>
+          <t>2929835</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2576761</t>
+          <t>2576342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2685988</t>
+          <t>2683684</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5450112</t>
+          <t>5454716</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5592195</t>
+          <t>5594245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,62%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2023</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129941</t>
+          <t>128395</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172813</t>
+          <t>172143</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>178611</t>
+          <t>182801</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>251120</t>
+          <t>252458</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>325607</t>
+          <t>333884</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>407840</t>
+          <t>409154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>462628</t>
+          <t>463298</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>505500</t>
+          <t>507046</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>474210</t>
+          <t>472872</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>546719</t>
+          <t>542529</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>952932</t>
+          <t>951618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1035165</t>
+          <t>1026888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80599</t>
+          <t>68977</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>199601</t>
+          <t>196898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>280232</t>
+          <t>277427</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>325733</t>
+          <t>324138</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>299879</t>
+          <t>299564</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>516190</t>
+          <t>520159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>993263</t>
+          <t>995966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1112265</t>
+          <t>1123887</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>632918</t>
+          <t>634513</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>678419</t>
+          <t>681224</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1635326</t>
+          <t>1631357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1851637</t>
+          <t>1851952</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101081</t>
+          <t>103669</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145537</t>
+          <t>146131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127917</t>
+          <t>109634</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>300621</t>
+          <t>300995</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>227577</t>
+          <t>234666</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>407374</t>
+          <t>409687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>559143</t>
+          <t>558549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>603599</t>
+          <t>601011</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>632745</t>
+          <t>632371</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>805449</t>
+          <t>823732</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1230672</t>
+          <t>1228359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1410469</t>
+          <t>1403380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,67%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153659</t>
+          <t>154453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>200358</t>
+          <t>196350</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>277434</t>
+          <t>283200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>383675</t>
+          <t>385433</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>460117</t>
+          <t>467695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>564357</t>
+          <t>566209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>726473</t>
+          <t>730481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>773172</t>
+          <t>772378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>711257</t>
+          <t>709499</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>817498</t>
+          <t>811732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1457406</t>
+          <t>1455554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1561646</t>
+          <t>1554068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>470623</t>
+          <t>457566</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>656562</t>
+          <t>659443</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>895754</t>
+          <t>872848</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1194646</t>
+          <t>1194874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1456828</t>
+          <t>1444766</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1814962</t>
+          <t>1814112</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2803255</t>
+          <t>2800374</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2989194</t>
+          <t>3002251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2517634</t>
+          <t>2517406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2816526</t>
+          <t>2839432</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5357135</t>
+          <t>5357985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5715269</t>
+          <t>5727331</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/POLIPATOLOGIA_Lim_2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/POLIPATOLOGIA_Lim_2-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108736</t>
+          <t>105424</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>152039</t>
+          <t>147805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>206858</t>
+          <t>203607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>256465</t>
+          <t>254082</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>325833</t>
+          <t>325291</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>392772</t>
+          <t>389760</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>551430</t>
+          <t>555664</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>594733</t>
+          <t>598045</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>440585</t>
+          <t>442968</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>490192</t>
+          <t>493443</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1007747</t>
+          <t>1010759</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1074686</t>
+          <t>1075228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>151594</t>
+          <t>151376</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>200868</t>
+          <t>201212</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>279617</t>
+          <t>279356</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>340335</t>
+          <t>340623</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>445783</t>
+          <t>449758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>526171</t>
+          <t>527320</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>817079</t>
+          <t>816735</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>866353</t>
+          <t>866571</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>691849</t>
+          <t>691561</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>752567</t>
+          <t>752828</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1523960</t>
+          <t>1522811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1604348</t>
+          <t>1600373</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,06%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91230</t>
+          <t>90233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133992</t>
+          <t>132760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>174180</t>
+          <t>173969</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>223471</t>
+          <t>226436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>279215</t>
+          <t>277288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>343222</t>
+          <t>345181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623631</t>
+          <t>624863</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666393</t>
+          <t>667390</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>553703</t>
+          <t>550738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>602994</t>
+          <t>603205</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1191575</t>
+          <t>1189616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1255582</t>
+          <t>1257509</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>144221</t>
+          <t>143567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>193174</t>
+          <t>195345</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>270174</t>
+          <t>269950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>332070</t>
+          <t>329378</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>430553</t>
+          <t>431117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>509160</t>
+          <t>512165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>754565</t>
+          <t>752394</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>803518</t>
+          <t>804172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>719831</t>
+          <t>722523</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>781727</t>
+          <t>781951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1490480</t>
+          <t>1487475</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1569087</t>
+          <t>1568523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>538765</t>
+          <t>536420</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>628083</t>
+          <t>633209</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>990630</t>
+          <t>987012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1099426</t>
+          <t>1089080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1554153</t>
+          <t>1545276</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1693328</t>
+          <t>1696504</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2798696</t>
+          <t>2793570</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2888014</t>
+          <t>2890359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2458883</t>
+          <t>2469229</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2567679</t>
+          <t>2571297</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5291760</t>
+          <t>5288584</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5430935</t>
+          <t>5439812</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85207</t>
+          <t>84232</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121846</t>
+          <t>121800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>167660</t>
+          <t>162502</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>214004</t>
+          <t>213846</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>261216</t>
+          <t>262368</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>323033</t>
+          <t>321726</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>552954</t>
+          <t>553000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>589593</t>
+          <t>590568</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>458835</t>
+          <t>458993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>505179</t>
+          <t>510337</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1024606</t>
+          <t>1025913</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1086423</t>
+          <t>1085271</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>130610</t>
+          <t>133541</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>175570</t>
+          <t>179792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>240631</t>
+          <t>243748</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>301966</t>
+          <t>304068</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>389068</t>
+          <t>386347</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>465250</t>
+          <t>463631</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>846861</t>
+          <t>842639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>891821</t>
+          <t>888890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>740947</t>
+          <t>738845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>802282</t>
+          <t>799165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1600094</t>
+          <t>1601713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1676276</t>
+          <t>1678997</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87705</t>
+          <t>85512</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124125</t>
+          <t>123337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>160184</t>
+          <t>158614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>205434</t>
+          <t>206393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256131</t>
+          <t>253082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>316322</t>
+          <t>318356</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>635427</t>
+          <t>636215</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>671847</t>
+          <t>674040</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>579577</t>
+          <t>578618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>624827</t>
+          <t>626397</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1228241</t>
+          <t>1226207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1288432</t>
+          <t>1291481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>125115</t>
+          <t>125990</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>170219</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>239501</t>
+          <t>240047</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>299518</t>
+          <t>303187</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>379464</t>
+          <t>377450</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>456355</t>
+          <t>453430</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>767348</t>
+          <t>768418</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>812452</t>
+          <t>811577</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>744261</t>
+          <t>740592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>804278</t>
+          <t>803732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1524991</t>
+          <t>1527916</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1601882</t>
+          <t>1603896</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>464515</t>
+          <t>465378</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>548687</t>
+          <t>550763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>860858</t>
+          <t>858479</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>968200</t>
+          <t>975038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1344647</t>
+          <t>1352608</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1484176</t>
+          <t>1490115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2845663</t>
+          <t>2843587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2929835</t>
+          <t>2928972</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2576342</t>
+          <t>2569504</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2683684</t>
+          <t>2686063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5454716</t>
+          <t>5448777</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5594245</t>
+          <t>5586284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,51%</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>149331</t>
+          <t>159524</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>128395</t>
+          <t>138093</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>172143</t>
+          <t>182625</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>225472</t>
+          <t>240778</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>182801</t>
+          <t>222482</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>252458</t>
+          <t>262057</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>374803</t>
+          <t>400302</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>333884</t>
+          <t>369515</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>409154</t>
+          <t>429907</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>486110</t>
+          <t>531186</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>463298</t>
+          <t>508085</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>507046</t>
+          <t>552617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>499858</t>
+          <t>493402</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>472872</t>
+          <t>472123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>542529</t>
+          <t>511698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>985969</t>
+          <t>1024587</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>951618</t>
+          <t>994982</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1026888</t>
+          <t>1055374</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148691</t>
+          <t>162627</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68977</t>
+          <t>140783</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>196898</t>
+          <t>187198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>301166</t>
+          <t>334189</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>277427</t>
+          <t>310989</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>324138</t>
+          <t>361197</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>449858</t>
+          <t>496817</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>299564</t>
+          <t>459439</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>520159</t>
+          <t>534603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1044173</t>
+          <t>886290</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>995966</t>
+          <t>861719</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1123887</t>
+          <t>908134</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>657485</t>
+          <t>737285</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>634513</t>
+          <t>710277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>681224</t>
+          <t>760485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1701658</t>
+          <t>1623574</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1631357</t>
+          <t>1585788</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1851952</t>
+          <t>1660952</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>121352</t>
+          <t>134894</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103669</t>
+          <t>115104</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146131</t>
+          <t>159939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>224042</t>
+          <t>257718</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109634</t>
+          <t>233358</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>300995</t>
+          <t>280389</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>345394</t>
+          <t>392612</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>234666</t>
+          <t>358795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>409687</t>
+          <t>425856</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>583328</t>
+          <t>668179</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>558549</t>
+          <t>643134</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>601011</t>
+          <t>687969</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>709324</t>
+          <t>554541</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>632371</t>
+          <t>531870</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>823732</t>
+          <t>578901</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1292652</t>
+          <t>1222720</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1228359</t>
+          <t>1189476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1403380</t>
+          <t>1256537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>77,79%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>175720</t>
+          <t>183947</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154453</t>
+          <t>161529</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196350</t>
+          <t>209418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>348923</t>
+          <t>376729</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>283200</t>
+          <t>350640</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>385433</t>
+          <t>404187</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>524643</t>
+          <t>560677</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>467695</t>
+          <t>522196</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>566209</t>
+          <t>595922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>751111</t>
+          <t>806115</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>730481</t>
+          <t>780644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>772378</t>
+          <t>828533</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>746009</t>
+          <t>742312</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>709499</t>
+          <t>714854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>811732</t>
+          <t>768401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1497120</t>
+          <t>1548427</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1455554</t>
+          <t>1513182</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1554068</t>
+          <t>1586908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>75,24%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>595095</t>
+          <t>640992</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>457566</t>
+          <t>597395</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>659443</t>
+          <t>691624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1099603</t>
+          <t>1209415</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>872848</t>
+          <t>1167141</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1194874</t>
+          <t>1265328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1694698</t>
+          <t>1850407</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1444766</t>
+          <t>1775947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1814112</t>
+          <t>1927855</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2864722</t>
+          <t>2891770</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2800374</t>
+          <t>2841138</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3002251</t>
+          <t>2935367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2612677</t>
+          <t>2527539</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2517406</t>
+          <t>2471626</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2839432</t>
+          <t>2569813</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5477399</t>
+          <t>5419309</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5357985</t>
+          <t>5341861</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5727331</t>
+          <t>5493769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>75,57%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
